--- a/artfynd/A 22426-2025 artfynd.xlsx
+++ b/artfynd/A 22426-2025 artfynd.xlsx
@@ -997,7 +997,7 @@
         <v>126679028</v>
       </c>
       <c r="B5" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>126679177</v>
       </c>
       <c r="B6" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 22426-2025 artfynd.xlsx
+++ b/artfynd/A 22426-2025 artfynd.xlsx
@@ -997,7 +997,7 @@
         <v>126679028</v>
       </c>
       <c r="B5" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>126679177</v>
       </c>
       <c r="B6" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 22426-2025 artfynd.xlsx
+++ b/artfynd/A 22426-2025 artfynd.xlsx
@@ -997,7 +997,7 @@
         <v>126679028</v>
       </c>
       <c r="B5" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>126679177</v>
       </c>
       <c r="B6" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 22426-2025 artfynd.xlsx
+++ b/artfynd/A 22426-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117140642</v>
+        <v>117140631</v>
       </c>
       <c r="B2" t="n">
-        <v>78444</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80305</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>392</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>606602</v>
+        <v>606374</v>
       </c>
       <c r="R2" t="n">
-        <v>6958843</v>
+        <v>6958998</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,6 +754,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117140632</v>
+        <v>117140628</v>
       </c>
       <c r="B3" t="n">
-        <v>79525</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>606465</v>
+        <v>606584</v>
       </c>
       <c r="R3" t="n">
-        <v>6958781</v>
+        <v>6958760</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,37 +878,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117140631</v>
+        <v>117140627</v>
       </c>
       <c r="B4" t="n">
-        <v>79398</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>392</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +913,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>606374</v>
+        <v>606584</v>
       </c>
       <c r="R4" t="n">
-        <v>6958998</v>
+        <v>6958757</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,7 +957,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -994,50 +979,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126679028</v>
+        <v>117140630</v>
       </c>
       <c r="B5" t="n">
-        <v>57741</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Killinghalsmyran, Mpd</t>
+          <t>Honkasosvedjan, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>606394</v>
+        <v>606602</v>
       </c>
       <c r="R5" t="n">
-        <v>6959030</v>
+        <v>6958843</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,17 +1044,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2024-05-19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>2024-05-19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1089,22 +1064,26 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126679177</v>
+        <v>117140629</v>
       </c>
       <c r="B6" t="n">
-        <v>57741</v>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1112,39 +1091,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Killinghalsmyran, Mpd</t>
+          <t>Honkasosvedjan, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>606438</v>
+        <v>606564</v>
       </c>
       <c r="R6" t="n">
-        <v>6958811</v>
+        <v>6958769</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1171,17 +1145,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2024-05-19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>2024-05-19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1196,15 +1165,542 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>117140632</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Honkasosvedjan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>606465</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6958781</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-05-19</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-05-19</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126679028</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Killinghalsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>606394</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6959030</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Joel Helker-Nygren</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>Joel Helker-Nygren</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126679177</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Killinghalsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>606438</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6958811</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126679223</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Killinghalsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>606439</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6958766</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126679721</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99155</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>223621</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Skogsnattviol</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia subsp. latiflora</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Killinghalsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>606395</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6958787</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22426-2025 artfynd.xlsx
+++ b/artfynd/A 22426-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117140631</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117140628</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -976,6 +991,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117140627</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1077,6 +1097,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117140630</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1178,6 +1203,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117140629</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1279,6 +1309,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117140632</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1386,6 +1421,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126679028</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1493,6 +1533,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126679177</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1600,6 +1645,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126679223</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1701,8 +1751,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126679721</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>